--- a/artfynd/A 50231-2023 artfynd.xlsx
+++ b/artfynd/A 50231-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50231-2023 artfynd.xlsx
+++ b/artfynd/A 50231-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87611507</v>
+        <v>114359440</v>
       </c>
       <c r="B2" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vid grustäkten, Stavre, Mpd</t>
+          <t>Ljustorpsån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623200</v>
+        <v>623245</v>
       </c>
       <c r="R2" t="n">
-        <v>6939427</v>
+        <v>6939484</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:01</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:01</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Sundin</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Sundin, Håkan Sundin</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -793,12 +775,7 @@
         <v>114359434</v>
       </c>
       <c r="B3" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114359433</v>
+        <v>114359436</v>
       </c>
       <c r="B4" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623202</v>
+        <v>623224</v>
       </c>
       <c r="R4" t="n">
-        <v>6939413</v>
+        <v>6939436</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,59 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114359443</v>
+        <v>114359437</v>
       </c>
       <c r="B5" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ljustorpsån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623204</v>
+        <v>623227</v>
       </c>
       <c r="R5" t="n">
-        <v>6939483</v>
+        <v>6939452</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-05-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>30x80 cm</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,59 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114359431</v>
+        <v>114359439</v>
       </c>
       <c r="B6" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ljustorpsån, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623166</v>
+        <v>623246</v>
       </c>
       <c r="R6" t="n">
-        <v>6939286</v>
+        <v>6939482</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1195,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-05-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>50x60 cm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114359445</v>
+        <v>114359441</v>
       </c>
       <c r="B7" t="n">
-        <v>96822</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220250</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1266,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623174</v>
+        <v>623244</v>
       </c>
       <c r="R7" t="n">
-        <v>6939463</v>
+        <v>6939485</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,6 +1254,964 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>87611507</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vid grustäkten, Stavre, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>623200</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6939427</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-08-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-08-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Eva Sundin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eva Sundin, Håkan Sundin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114359435</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ljustorpsån, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>623218</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6939413</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114359433</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ljustorpsån, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>623202</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6939413</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>94876011</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58435</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100058</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ficedula parva</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1794)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tågmon, Ljustorpsån, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>623170</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6939504</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-07-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-07-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114359445</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ljustorpsån, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>623174</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6939463</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114359431</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ljustorpsån, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>623166</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6939286</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>50x60 cm</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114359438</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ljustorpsån, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>623243</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6939453</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>30x20 cm</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114359442</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ljustorpsån, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>623230</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6939481</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>20x100 cm</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114359443</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ljustorpsån, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>623204</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6939483</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hässjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>30x80 cm</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50231-2023 artfynd.xlsx
+++ b/artfynd/A 50231-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359440</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359434</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359436</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359437</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359439</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359441</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,6 +1399,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87611507</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359435</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1558,6 +1603,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359433</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1671,6 +1721,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94876011</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1768,6 +1823,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359445</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1879,6 +1939,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359431</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359438</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2101,6 +2171,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359442</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2212,8 +2287,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114359443</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>